--- a/datasets/dict/dict_ps_df004.xlsx
+++ b/datasets/dict/dict_ps_df004.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" state="visible" r:id="rId1"/>
@@ -740,7 +740,7 @@
           <t>rs_ps_df004_d01</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>rs_ps_df004_v01</t>
         </is>

--- a/datasets/dict/dict_ps_df004.xlsx
+++ b/datasets/dict/dict_ps_df004.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DC3DA8BE92017B561A6983E4DE6EB7ACE352C917" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55EA36C4-DEE7-3E4E-A300-A337FC75D1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,9 +29,141 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
+    <t>e_id</t>
+  </si>
+  <si>
+    <t>canonical_form</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
     <t>ps_id</t>
   </si>
   <si>
+    <t>난이도</t>
+  </si>
+  <si>
+    <t>주제</t>
+  </si>
+  <si>
+    <t>gloss</t>
+  </si>
+  <si>
+    <t>df004</t>
+  </si>
+  <si>
+    <t>고 말1</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>ps_df004</t>
+  </si>
+  <si>
+    <t>일어나지 않았으면 좋았을 어떤 일이 끝내 일어났음을 나타내며 동시에 그 일이 일어난 것에 대한 화자의 안타까움을 나타낼 때 쓴다.</t>
+  </si>
+  <si>
+    <t>df005</t>
+  </si>
+  <si>
+    <t>고 말2</t>
+  </si>
+  <si>
+    <t>이루기 쉽지 않은 어떤 일을 이루고자 하는 화자의 의지를 나타낼 때 쓴다.</t>
+  </si>
+  <si>
+    <t>primary_e_id</t>
+  </si>
+  <si>
+    <t>member_e_ids</t>
+  </si>
+  <si>
+    <t>ps_canonical_form</t>
+  </si>
+  <si>
+    <t>disconti_allowed</t>
+  </si>
+  <si>
+    <t>ps_comp_id</t>
+  </si>
+  <si>
+    <t>detect_ruleset_id</t>
+  </si>
+  <si>
+    <t>verify_ruleset_id</t>
+  </si>
+  <si>
+    <t>gloss_intro</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>df004;df005</t>
+  </si>
+  <si>
+    <t>고 말</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>c1;c2</t>
+  </si>
+  <si>
+    <t>rs_ps_df004_d01</t>
+  </si>
+  <si>
+    <t>rs_ps_df004_v01</t>
+  </si>
+  <si>
+    <t>다음 의미를 포함하는 문법항목:</t>
+  </si>
+  <si>
+    <t>comp_surf</t>
+  </si>
+  <si>
+    <t>comp_id</t>
+  </si>
+  <si>
+    <t>bridge_id</t>
+  </si>
+  <si>
+    <t>is_required</t>
+  </si>
+  <si>
+    <t>anchor_rank</t>
+  </si>
+  <si>
+    <t>comp_order</t>
+  </si>
+  <si>
+    <t>order_policy</t>
+  </si>
+  <si>
+    <t>min_gap_to_next</t>
+  </si>
+  <si>
+    <t>max_gap_to_next</t>
+  </si>
+  <si>
+    <t>고</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>fx</t>
+  </si>
+  <si>
+    <t>말</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
     <t>ruleset_id</t>
   </si>
   <si>
@@ -65,12 +197,6 @@
     <t>rule_note</t>
   </si>
   <si>
-    <t>ps_df004</t>
-  </si>
-  <si>
-    <t>rs_ps_df004_d01</t>
-  </si>
-  <si>
     <t>r_ps_df004_d01</t>
   </si>
   <si>
@@ -89,9 +215,6 @@
     <t>bootstrap detect rule for 고 말 / 고야 말 recall loop</t>
   </si>
   <si>
-    <t>rs_ps_df004_v01</t>
-  </si>
-  <si>
     <t>r_ps_df004_v01</t>
   </si>
   <si>
@@ -101,15 +224,9 @@
     <t>component_left_context</t>
   </si>
   <si>
-    <t>c1</t>
-  </si>
-  <si>
     <t>^(?:다"|”라)$</t>
   </si>
   <si>
-    <t>y</t>
-  </si>
-  <si>
     <t>hard fail quoted speech contexts immediately left of 고 말: 다" / ”라</t>
   </si>
   <si>
@@ -119,127 +236,10 @@
     <t>component_right_context</t>
   </si>
   <si>
-    <t>c2</t>
-  </si>
-  <si>
-    <t>^(?:했|해|을|하|씀)$</t>
-  </si>
-  <si>
-    <t>hard fail speech-verb/nominal contexts immediately right of 말: 했/해/을/하/씀</t>
-  </si>
-  <si>
-    <t>e_id</t>
-  </si>
-  <si>
-    <t>canonical_form</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>난이도</t>
-  </si>
-  <si>
-    <t>주제</t>
-  </si>
-  <si>
-    <t>gloss</t>
-  </si>
-  <si>
-    <t>df004</t>
-  </si>
-  <si>
-    <t>고 말1</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>일어나지 않았으면 좋았을 어떤 일이 끝내 일어났음을 나타내며 동시에 그 일이 일어난 것에 대한 화자의 안타까움을 나타낼 때 쓴다.</t>
-  </si>
-  <si>
-    <t>df005</t>
-  </si>
-  <si>
-    <t>고 말2</t>
-  </si>
-  <si>
-    <t>이루기 쉽지 않은 어떤 일을 이루고자 하는 화자의 의지를 나타낼 때 쓴다.</t>
-  </si>
-  <si>
-    <t>primary_e_id</t>
-  </si>
-  <si>
-    <t>member_e_ids</t>
-  </si>
-  <si>
-    <t>ps_canonical_form</t>
-  </si>
-  <si>
-    <t>disconti_allowed</t>
-  </si>
-  <si>
-    <t>ps_comp_id</t>
-  </si>
-  <si>
-    <t>detect_ruleset_id</t>
-  </si>
-  <si>
-    <t>verify_ruleset_id</t>
-  </si>
-  <si>
-    <t>gloss_intro</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>df004;df005</t>
-  </si>
-  <si>
-    <t>고 말</t>
-  </si>
-  <si>
-    <t>c1;c2</t>
-  </si>
-  <si>
-    <t>다음 의미를 포함하는 문법항목:</t>
-  </si>
-  <si>
-    <t>comp_surf</t>
-  </si>
-  <si>
-    <t>comp_id</t>
-  </si>
-  <si>
-    <t>bridge_id</t>
-  </si>
-  <si>
-    <t>is_required</t>
-  </si>
-  <si>
-    <t>anchor_rank</t>
-  </si>
-  <si>
-    <t>comp_order</t>
-  </si>
-  <si>
-    <t>order_policy</t>
-  </si>
-  <si>
-    <t>min_gap_to_next</t>
-  </si>
-  <si>
-    <t>max_gap_to_next</t>
-  </si>
-  <si>
-    <t>고</t>
-  </si>
-  <si>
-    <t>fx</t>
-  </si>
-  <si>
-    <t>말</t>
+    <t>^(?:했|해|을|하|씀|할|은|도|린|들|지|안|로|이)$</t>
+  </si>
+  <si>
+    <t>hard fail speech-verb/nominal contexts immediately right of 말: 했/해/을/하/씀/할/은/도/린/들/지/안/로/이</t>
   </si>
 </sst>
 </file>
@@ -696,59 +696,59 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="19" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -778,63 +778,63 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -860,45 +860,45 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
@@ -911,18 +911,18 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
@@ -935,7 +935,7 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +956,7 @@
     <col min="4" max="4" width="10.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="5" customWidth="1"/>
     <col min="6" max="7" width="16.42578125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" style="5" customWidth="1"/>
     <col min="9" max="9" width="9" style="2" customWidth="1"/>
     <col min="10" max="11" width="15.85546875" style="5" customWidth="1"/>
     <col min="12" max="12" width="65.28515625" style="5" bestFit="1" customWidth="1"/>
@@ -964,96 +964,96 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="K2"/>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="K3"/>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="I4">
         <v>20</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K4"/>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
